--- a/PPG/Avaliação CAPES.xlsx
+++ b/PPG/Avaliação CAPES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03847DC7-CC94-B044-98E6-EDE41DA36844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E7D93C-F48D-9A48-BE12-144071702DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1640" yWindow="1600" windowWidth="27160" windowHeight="16400" activeTab="1" xr2:uid="{D63A89C5-1CF9-944C-B99E-829D01D159A4}"/>
+    <workbookView xWindow="1640" yWindow="1600" windowWidth="27160" windowHeight="16400" xr2:uid="{D63A89C5-1CF9-944C-B99E-829D01D159A4}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-2028" sheetId="6" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
   <si>
     <t>Resolução No. 2/2007 CEPE-UNISUAM.pdf</t>
   </si>
@@ -190,6 +190,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1uripSQ5e7XZrhl2EZHf2sywDgRMhQZRB</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PfOER-y7tVlAZeg1lbPo_rnWNSQD9luy</t>
+  </si>
+  <si>
+    <t>Portaria No. 32-2026.pdf</t>
   </si>
 </sst>
 </file>
@@ -564,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C017908A-A8F5-E649-8963-5ABAE14D9B0D}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="3" bestFit="1" customWidth="1"/>
@@ -585,13 +594,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -599,16 +608,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{683CAB6B-BD90-DA4E-AC21-93BF953827E8}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{4F23CA3F-8F45-034D-8201-C3B9D60A7DBC}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{683CAB6B-BD90-DA4E-AC21-93BF953827E8}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{4F23CA3F-8F45-034D-8201-C3B9D60A7DBC}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{258D9911-E7FC-574A-AAD9-505ACC056126}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
